--- a/Assets/ExcelData/DropTable.xlsx
+++ b/Assets/ExcelData/DropTable.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F6821F-9AC5-4E06-9B4F-7C3AD559FA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961B9B60-E57A-4A77-844B-4F6986A90513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DropTable" sheetId="1" r:id="rId1"/>
     <sheet name="DropEntry" sheetId="2" r:id="rId2"/>
+    <sheet name="DungeonTable" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,85 +38,120 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>DropTable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TableName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
   <si>
     <t>Rolls</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>FieldMonsterNormal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonClear_Easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonClear_Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonClear_Hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossClear_Easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossClear_Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossClear_Hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldMonsterElite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>DropTableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardType</t>
   </si>
   <si>
     <t>ItemID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tier</t>
   </si>
   <si>
     <t>Weight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MinCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MaxCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tier</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RewardType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FieldMonsterNormal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonClear_Easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonClear_Normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonClear_Hard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BossClear_Easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BossClear_Normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BossClear_Hard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FieldMonsterElite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Equipment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Material</t>
+  </si>
+  <si>
+    <t>DungeonID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearCredit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearDropTableID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒷골목_쉬움</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒷골목_보통</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒷골목_어려움</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예로니무스 보스전_쉬움</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예로니무스 보스전_보통</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예로니무스 보스전_어려움</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropTableID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropTableName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -454,13 +490,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -468,10 +504,10 @@
         <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
         <v>10</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -479,7 +515,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -490,7 +526,7 @@
         <v>201</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
@@ -501,7 +537,7 @@
         <v>202</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
         <v>7</v>
@@ -512,7 +548,7 @@
         <v>203</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -523,7 +559,7 @@
         <v>301</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1">
         <v>10</v>
@@ -534,7 +570,7 @@
         <v>302</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1">
         <v>15</v>
@@ -545,7 +581,7 @@
         <v>303</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1">
         <v>20</v>
@@ -559,7 +595,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A2F2CD-D57D-4AC6-842C-76621A6FC4D8}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="13" customWidth="1"/>
@@ -571,25 +607,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -597,13 +633,17 @@
         <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C2" s="1">
+        <v>-1</v>
+      </c>
       <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>500</v>
+      </c>
       <c r="F2" s="1">
         <v>1</v>
       </c>
@@ -616,13 +656,17 @@
         <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C3" s="1">
+        <v>-1</v>
+      </c>
       <c r="D3" s="1">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="E3" s="1">
+        <v>500</v>
+      </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
@@ -635,7 +679,7 @@
         <v>101</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1">
         <v>30000</v>
@@ -643,7 +687,9 @@
       <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1">
+        <v>10</v>
+      </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
@@ -656,7 +702,7 @@
         <v>101</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>30003</v>
@@ -664,7 +710,9 @@
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1">
+        <v>10</v>
+      </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
@@ -673,49 +721,1268 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="A6" s="1">
+        <v>102</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="A7" s="1">
+        <v>102</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="A8" s="1">
+        <v>102</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1">
+        <v>30000</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="A9" s="1">
+        <v>102</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30003</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="A10" s="1">
+        <v>102</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30004</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>201</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>201</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1">
+        <v>5</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>201</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>201</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1">
+        <v>30000</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>201</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1">
+        <v>30003</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>201</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1">
+        <v>30004</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>202</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>4</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>202</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>202</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="1">
+        <v>6</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>202</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="1">
+        <v>30000</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>6</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>202</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1">
+        <v>30003</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>8</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>202</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="1">
+        <v>30004</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>8</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>202</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="1">
+        <v>30005</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>203</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>5</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>203</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D25" s="1">
+        <v>6</v>
+      </c>
+      <c r="E25" s="1">
+        <v>5</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>203</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>7</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>203</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D27" s="1">
+        <v>8</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>203</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="1">
+        <v>30000</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>5</v>
+      </c>
+      <c r="F28" s="1">
+        <v>5</v>
+      </c>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>203</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="1">
+        <v>30003</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>6</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>203</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="1">
+        <v>30004</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>203</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="1">
+        <v>30005</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>6</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>301</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D32" s="1">
+        <v>5</v>
+      </c>
+      <c r="E32" s="1">
+        <v>5</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>301</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D33" s="1">
+        <v>6</v>
+      </c>
+      <c r="E33" s="1">
+        <v>5</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>301</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D34" s="1">
+        <v>7</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>301</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="1">
+        <v>30000</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>5</v>
+      </c>
+      <c r="F35" s="1">
+        <v>5</v>
+      </c>
+      <c r="G35" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>301</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="1">
+        <v>30003</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>6</v>
+      </c>
+      <c r="F36" s="1">
+        <v>3</v>
+      </c>
+      <c r="G36" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>301</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="1">
+        <v>30004</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>7</v>
+      </c>
+      <c r="F37" s="1">
+        <v>2</v>
+      </c>
+      <c r="G37" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>301</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="1">
+        <v>30005</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>5</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>302</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D39" s="1">
+        <v>6</v>
+      </c>
+      <c r="E39" s="1">
+        <v>5</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>302</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D40" s="1">
+        <v>7</v>
+      </c>
+      <c r="E40" s="1">
+        <v>5</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>302</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D41" s="1">
+        <v>8</v>
+      </c>
+      <c r="E41" s="1">
+        <v>5</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>302</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D42" s="1">
+        <v>9</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>302</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="1">
+        <v>30000</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1">
+        <v>4</v>
+      </c>
+      <c r="F43" s="1">
+        <v>8</v>
+      </c>
+      <c r="G43" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>302</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="1">
+        <v>30003</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
+        <v>6</v>
+      </c>
+      <c r="F44" s="1">
+        <v>5</v>
+      </c>
+      <c r="G44" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>302</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="1">
+        <v>30004</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1">
+        <v>8</v>
+      </c>
+      <c r="F45" s="1">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>302</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="1">
+        <v>30005</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1">
+        <v>6</v>
+      </c>
+      <c r="F46" s="1">
+        <v>2</v>
+      </c>
+      <c r="G46" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>303</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D47" s="1">
+        <v>7</v>
+      </c>
+      <c r="E47" s="1">
+        <v>5</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>303</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D48" s="1">
+        <v>8</v>
+      </c>
+      <c r="E48" s="1">
+        <v>5</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>303</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D49" s="1">
+        <v>9</v>
+      </c>
+      <c r="E49" s="1">
+        <v>5</v>
+      </c>
+      <c r="F49" s="1">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>303</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="1">
+        <v>-1</v>
+      </c>
+      <c r="D50" s="1">
+        <v>10</v>
+      </c>
+      <c r="E50" s="1">
+        <v>3</v>
+      </c>
+      <c r="F50" s="1">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>303</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="1">
+        <v>30000</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1">
+        <v>3</v>
+      </c>
+      <c r="F51" s="1">
+        <v>10</v>
+      </c>
+      <c r="G51" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>303</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="1">
+        <v>30003</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1">
+        <v>5</v>
+      </c>
+      <c r="F52" s="1">
+        <v>8</v>
+      </c>
+      <c r="G52" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>303</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="1">
+        <v>30004</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1">
+        <v>8</v>
+      </c>
+      <c r="F53" s="1">
+        <v>5</v>
+      </c>
+      <c r="G53" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>303</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="1">
+        <v>30005</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="1">
+        <v>8</v>
+      </c>
+      <c r="F54" s="1">
+        <v>3</v>
+      </c>
+      <c r="G54" s="1">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7FCA26-5278-48D5-9A50-96E676EC1DB8}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.375" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1">
+        <v>500</v>
+      </c>
+      <c r="D2" s="1">
+        <v>10000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1">
+        <v>600</v>
+      </c>
+      <c r="D3" s="1">
+        <v>12000</v>
+      </c>
+      <c r="E3" s="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1">
+        <v>800</v>
+      </c>
+      <c r="D4" s="1">
+        <v>20000</v>
+      </c>
+      <c r="E4" s="1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="1">
+        <v>30000</v>
+      </c>
+      <c r="E5" s="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D6" s="1">
+        <v>40000</v>
+      </c>
+      <c r="E6" s="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="1">
+        <v>50000</v>
+      </c>
+      <c r="E7" s="1">
+        <v>303</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/ExcelData/DropTable.xlsx
+++ b/Assets/ExcelData/DropTable.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961B9B60-E57A-4A77-844B-4F6986A90513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F9431F-E1DB-4960-814B-0F4C16746E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DropTable" sheetId="1" r:id="rId1"/>
     <sheet name="DropEntry" sheetId="2" r:id="rId2"/>
-    <sheet name="DungeonTable" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="20">
   <si>
     <t>Rolls</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,50 +100,6 @@
   </si>
   <si>
     <t>Material</t>
-  </si>
-  <si>
-    <t>DungeonID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClearExp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClearCredit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClearDropTableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒷골목_쉬움</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒷골목_보통</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒷골목_어려움</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예로니무스 보스전_쉬움</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예로니무스 보스전_보통</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예로니무스 보스전_어려움</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>DropTableID</t>
@@ -490,10 +445,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1851,141 +1806,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7FCA26-5278-48D5-9A50-96E676EC1DB8}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.375" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1000</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1">
-        <v>500</v>
-      </c>
-      <c r="D2" s="1">
-        <v>10000</v>
-      </c>
-      <c r="E2" s="1">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>1001</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="1">
-        <v>600</v>
-      </c>
-      <c r="D3" s="1">
-        <v>12000</v>
-      </c>
-      <c r="E3" s="1">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1">
-        <v>800</v>
-      </c>
-      <c r="D4" s="1">
-        <v>20000</v>
-      </c>
-      <c r="E4" s="1">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>1003</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D5" s="1">
-        <v>30000</v>
-      </c>
-      <c r="E5" s="1">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>1004</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D6" s="1">
-        <v>40000</v>
-      </c>
-      <c r="E6" s="1">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>1005</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3000</v>
-      </c>
-      <c r="D7" s="1">
-        <v>50000</v>
-      </c>
-      <c r="E7" s="1">
-        <v>303</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>